--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92439</v>
+        <v>92441</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92446</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>135851121</v>
       </c>
       <c r="B9" t="n">
-        <v>5484</v>
+        <v>5485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>135851125</v>
       </c>
       <c r="B10" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135851124</v>
       </c>
       <c r="B11" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135851061</v>
       </c>
       <c r="B12" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135851069</v>
       </c>
       <c r="B13" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135851108</v>
       </c>
       <c r="B14" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135851112</v>
       </c>
       <c r="B15" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135851115</v>
       </c>
       <c r="B16" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135851120</v>
       </c>
       <c r="B17" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135851065</v>
       </c>
       <c r="B18" t="n">
-        <v>40308</v>
+        <v>40310</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>135851110</v>
       </c>
       <c r="B19" t="n">
-        <v>40308</v>
+        <v>40310</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135851044</v>
       </c>
       <c r="B21" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>135851035</v>
       </c>
       <c r="B22" t="n">
-        <v>5181</v>
+        <v>5182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>135851056</v>
       </c>
       <c r="B23" t="n">
-        <v>5180</v>
+        <v>5181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>135851048</v>
       </c>
       <c r="B24" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>135851045</v>
       </c>
       <c r="B25" t="n">
-        <v>58136</v>
+        <v>58138</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>135851007</v>
       </c>
       <c r="B26" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>135851009</v>
       </c>
       <c r="B27" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>135851015</v>
       </c>
       <c r="B28" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
         <v>135851057</v>
       </c>
       <c r="B29" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92441</v>
+        <v>92455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92455</v>
+        <v>92456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92461</v>
+        <v>92462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92462</v>
+        <v>92463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>135851125</v>
       </c>
       <c r="B10" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135851124</v>
       </c>
       <c r="B11" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135851044</v>
       </c>
       <c r="B21" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>135851048</v>
       </c>
       <c r="B24" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>135851045</v>
       </c>
       <c r="B25" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92463</v>
+        <v>92469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>135851125</v>
       </c>
       <c r="B10" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135851124</v>
       </c>
       <c r="B11" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135851044</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>135851048</v>
       </c>
       <c r="B24" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>135851045</v>
       </c>
       <c r="B25" t="n">
-        <v>58139</v>
+        <v>58143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92458</v>
+        <v>92464</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92469</v>
+        <v>92470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>135851125</v>
       </c>
       <c r="B10" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135851124</v>
       </c>
       <c r="B11" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135851044</v>
       </c>
       <c r="B21" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>135851048</v>
       </c>
       <c r="B24" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>135851045</v>
       </c>
       <c r="B25" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92464</v>
+        <v>92465</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92470</v>
+        <v>92476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92465</v>
+        <v>92471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92476</v>
+        <v>92483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>135851125</v>
       </c>
       <c r="B10" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135851124</v>
       </c>
       <c r="B11" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135851065</v>
       </c>
       <c r="B18" t="n">
-        <v>40310</v>
+        <v>40315</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>135851110</v>
       </c>
       <c r="B19" t="n">
-        <v>40310</v>
+        <v>40315</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135851044</v>
       </c>
       <c r="B21" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>135851048</v>
       </c>
       <c r="B24" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>135851045</v>
       </c>
       <c r="B25" t="n">
-        <v>58144</v>
+        <v>58149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92471</v>
+        <v>92478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92483</v>
+        <v>92484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92478</v>
+        <v>92479</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92484</v>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>135851125</v>
       </c>
       <c r="B10" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>135851124</v>
       </c>
       <c r="B11" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135851065</v>
       </c>
       <c r="B18" t="n">
-        <v>40315</v>
+        <v>40328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>135851110</v>
       </c>
       <c r="B19" t="n">
-        <v>40315</v>
+        <v>40328</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>135851044</v>
       </c>
       <c r="B21" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>135851048</v>
       </c>
       <c r="B24" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>135851045</v>
       </c>
       <c r="B25" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92479</v>
+        <v>92492</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49142-2023 artfynd.xlsx
+++ b/artfynd/A 49142-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135851060</v>
       </c>
       <c r="B2" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>135851040</v>
       </c>
       <c r="B3" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>135851073</v>
       </c>
       <c r="B4" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135851041</v>
       </c>
       <c r="B5" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>135851059</v>
       </c>
       <c r="B6" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135851064</v>
       </c>
       <c r="B7" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>135851116</v>
       </c>
       <c r="B8" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>135851017</v>
       </c>
       <c r="B20" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>135851055</v>
       </c>
       <c r="B30" t="n">
-        <v>92492</v>
+        <v>92493</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
